--- a/assets/ご記入シート.xlsx
+++ b/assets/ご記入シート.xlsx
@@ -656,7 +656,7 @@
     <row r="16" ht="52" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　https://morikosha.com/ で、淡・玄・雅・粋・理の5案をご覧いただけます。どれを選んでも、載る項目は同じです。「希望デザイン」の欄に案名をお書きください。</t>
+          <t xml:space="preserve">　https://morikosha.com/ で、淡（あわい）・玄（げん）・雅（みやび）・粋（いき）・理（り）の5案をご覧いただけます。どれを選んでも、載る項目は同じです。「希望デザイン」の欄にお書きください。</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">morikosha.com で5案（淡・玄・雅・粋・理）の実物をご覧いただけます。「理」または「5案「理」」のようにお書きください。載る項目は、どの案も同じです。</t>
+          <t>morikosha.com で5案（淡・玄・雅・粋・理）の実物をご覧いただけます。「1案「淡」」のようにお書きください。載る項目は、どの案も同じです。</t>
         </is>
       </c>
     </row>
